--- a/documents/Comparativa final.xlsx
+++ b/documents/Comparativa final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cromi\Desktop\TFM GitHub\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3897CED-6A1A-47B0-B284-D3B5179AC9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE14DB2-CD01-486B-BDE1-1E9456E105AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ACD737A7-70F8-428B-B412-8894FB022ABE}"/>
+    <workbookView xWindow="-28935" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{ACD737A7-70F8-428B-B412-8894FB022ABE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
   <si>
     <t>Familia Algorítmica</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>Indistinto</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Estadísticos Multivar.</t>
@@ -124,9 +121,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +156,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -180,7 +183,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -337,21 +340,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFCBD5E0"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCBD5E0"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCBD5E0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCBD5E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FFCBD5E0"/>
       </left>
@@ -398,21 +386,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFCBD5E0"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCBD5E0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCBD5E0"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCBD5E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color rgb="FFCBD5E0"/>
       </left>
@@ -421,19 +394,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCBD5E0"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCBD5E0"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFCBD5E0"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -451,7 +411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -468,28 +428,16 @@
     <xf numFmtId="4" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -498,33 +446,12 @@
     <xf numFmtId="4" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -543,14 +470,1219 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="107">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF6790E3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-9.9948118533890809E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -565,6 +1697,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF6790E3"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -893,7 +2030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D4A0A5-E9A7-4425-8173-B85FDDAC066A}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
@@ -908,35 +2045,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="24" t="s">
+      <c r="E1" s="20"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="31"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="24" t="s">
+      <c r="H1" s="14"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="31"/>
-      <c r="L1" s="32"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="27"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="18"/>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
@@ -965,7 +2102,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -981,8 +2118,8 @@
       <c r="E3" s="5">
         <v>575.42999999999995</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>12</v>
+      <c r="F3" s="28">
+        <v>0.82250000000000001</v>
       </c>
       <c r="G3" s="5">
         <v>945.84</v>
@@ -990,7 +2127,7 @@
       <c r="H3" s="5">
         <v>578.34</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="28">
         <v>0.75239999999999996</v>
       </c>
       <c r="J3" s="5">
@@ -999,585 +2136,590 @@
       <c r="K3" s="5">
         <v>440.51</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="28">
         <v>0.82889999999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="C4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7">
+        <v>518.14</v>
+      </c>
+      <c r="E4" s="7">
+        <v>348.94</v>
+      </c>
+      <c r="F4" s="29">
+        <v>0.92520000000000002</v>
+      </c>
+      <c r="G4" s="7">
+        <v>895.14</v>
+      </c>
+      <c r="H4" s="7">
+        <v>659.39</v>
+      </c>
+      <c r="I4" s="29">
+        <v>0.77839999999999998</v>
+      </c>
+      <c r="J4" s="7">
+        <v>939.49</v>
+      </c>
+      <c r="K4" s="7">
+        <v>716.55</v>
+      </c>
+      <c r="L4" s="29">
+        <v>0.75470000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="23"/>
+      <c r="B5" s="26"/>
+      <c r="C5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="8">
-        <v>724.98</v>
-      </c>
-      <c r="E4" s="8">
-        <v>724.98</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="8">
-        <v>1997.87</v>
-      </c>
-      <c r="H4" s="8">
-        <v>1656.96</v>
-      </c>
-      <c r="I4" s="9">
-        <v>-1.7306999999999999</v>
-      </c>
-      <c r="J4" s="8">
-        <v>1162.31</v>
-      </c>
-      <c r="K4" s="8">
-        <v>897.68</v>
-      </c>
-      <c r="L4" s="10">
-        <v>0.50370000000000004</v>
+      <c r="D5" s="9">
+        <v>518.14</v>
+      </c>
+      <c r="E5" s="9">
+        <v>348.94</v>
+      </c>
+      <c r="F5" s="30">
+        <v>0.92520000000000002</v>
+      </c>
+      <c r="G5" s="9">
+        <v>895.14</v>
+      </c>
+      <c r="H5" s="9">
+        <v>659.39</v>
+      </c>
+      <c r="I5" s="30">
+        <v>0.77839999999999998</v>
+      </c>
+      <c r="J5" s="9">
+        <v>939.49</v>
+      </c>
+      <c r="K5" s="9">
+        <v>716.55</v>
+      </c>
+      <c r="L5" s="30">
+        <v>0.75470000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="19"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="11" t="s">
+    <row r="6" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23"/>
+      <c r="B6" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="12">
-        <v>724.98</v>
-      </c>
-      <c r="E5" s="12">
-        <v>724.98</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="12">
-        <v>1997.87</v>
-      </c>
-      <c r="H5" s="12">
-        <v>1656.96</v>
-      </c>
-      <c r="I5" s="12">
-        <v>-1.7306999999999999</v>
-      </c>
-      <c r="J5" s="12">
-        <v>1162.31</v>
-      </c>
-      <c r="K5" s="12">
-        <v>897.68</v>
-      </c>
-      <c r="L5" s="13">
-        <v>0.50370000000000004</v>
+      <c r="C6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="7">
+        <v>426.92500000000001</v>
+      </c>
+      <c r="E6" s="7">
+        <v>294.21749999999997</v>
+      </c>
+      <c r="F6" s="29">
+        <v>0.949125</v>
+      </c>
+      <c r="G6" s="7">
+        <v>698.76249999999993</v>
+      </c>
+      <c r="H6" s="7">
+        <v>497.73750000000001</v>
+      </c>
+      <c r="I6" s="29">
+        <v>0.86455000000000004</v>
+      </c>
+      <c r="J6" s="7">
+        <v>802.71500000000003</v>
+      </c>
+      <c r="K6" s="7">
+        <v>620.83500000000004</v>
+      </c>
+      <c r="L6" s="29">
+        <v>0.8206</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="19"/>
-      <c r="B6" s="21" t="s">
+    <row r="7" spans="1:13" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="23"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="32">
+        <v>400.68000000000012</v>
+      </c>
+      <c r="E7" s="32">
+        <v>273.36750000000001</v>
+      </c>
+      <c r="F7" s="33">
+        <v>0.95510000000000006</v>
+      </c>
+      <c r="G7" s="32">
+        <v>613.18999999999994</v>
+      </c>
+      <c r="H7" s="32">
+        <v>423.91500000000002</v>
+      </c>
+      <c r="I7" s="33">
+        <v>0.89575000000000005</v>
+      </c>
+      <c r="J7" s="32">
+        <v>664.11750000000006</v>
+      </c>
+      <c r="K7" s="32">
+        <v>462.36250000000001</v>
+      </c>
+      <c r="L7" s="33">
+        <v>0.87717500000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="23"/>
+      <c r="B8" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="11">
+        <v>426.92</v>
+      </c>
+      <c r="E8" s="11">
+        <v>294.22000000000003</v>
+      </c>
+      <c r="F8" s="31">
+        <v>0.94910000000000005</v>
+      </c>
+      <c r="G8" s="11">
+        <v>698.76</v>
+      </c>
+      <c r="H8" s="11">
+        <v>497.74</v>
+      </c>
+      <c r="I8" s="31">
+        <v>0.86460000000000004</v>
+      </c>
+      <c r="J8" s="11">
+        <v>802.72</v>
+      </c>
+      <c r="K8" s="11">
+        <v>620.84</v>
+      </c>
+      <c r="L8" s="31">
+        <v>0.8206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="24"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="8">
-        <v>136.96</v>
-      </c>
-      <c r="E6" s="8">
-        <v>136.96</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="8">
-        <v>1586.18</v>
-      </c>
-      <c r="H6" s="8">
-        <v>1228.45</v>
-      </c>
-      <c r="I6" s="9">
-        <v>-0.68740000000000001</v>
-      </c>
-      <c r="J6" s="8">
-        <v>1008.04</v>
-      </c>
-      <c r="K6" s="8">
-        <v>768.91</v>
-      </c>
-      <c r="L6" s="10">
-        <v>0.63080000000000003</v>
+      <c r="D9" s="32">
+        <v>400.68</v>
+      </c>
+      <c r="E9" s="32">
+        <v>273.37</v>
+      </c>
+      <c r="F9" s="33">
+        <v>0.95509999999999995</v>
+      </c>
+      <c r="G9" s="32">
+        <v>613.19000000000005</v>
+      </c>
+      <c r="H9" s="32">
+        <v>423.92</v>
+      </c>
+      <c r="I9" s="33">
+        <v>0.89570000000000005</v>
+      </c>
+      <c r="J9" s="32">
+        <v>664.12</v>
+      </c>
+      <c r="K9" s="32">
+        <v>462.36</v>
+      </c>
+      <c r="L9" s="33">
+        <v>0.87719999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="19"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="12">
-        <v>336.05</v>
-      </c>
-      <c r="E7" s="12">
-        <v>336.05</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="12">
-        <v>1239.6199999999999</v>
-      </c>
-      <c r="H7" s="12">
-        <v>913.65</v>
-      </c>
-      <c r="I7" s="12">
-        <v>-5.04E-2</v>
-      </c>
-      <c r="J7" s="12">
-        <v>843.16</v>
-      </c>
-      <c r="K7" s="12">
-        <v>591.34</v>
-      </c>
-      <c r="L7" s="13">
-        <v>0.73719999999999997</v>
+    <row r="10" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="34">
+        <v>432.05</v>
+      </c>
+      <c r="E10" s="34">
+        <v>295.83999999999997</v>
+      </c>
+      <c r="F10" s="35">
+        <v>0.94830000000000003</v>
+      </c>
+      <c r="G10" s="7">
+        <v>614</v>
+      </c>
+      <c r="H10" s="7">
+        <v>516.67999999999995</v>
+      </c>
+      <c r="I10" s="29">
+        <v>0.74709999999999999</v>
+      </c>
+      <c r="J10" s="7">
+        <v>911.19</v>
+      </c>
+      <c r="K10" s="7">
+        <v>694.07</v>
+      </c>
+      <c r="L10" s="29">
+        <v>0.69989999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
-      <c r="B8" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="14" t="s">
+    <row r="11" spans="1:13" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="23"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="15">
-        <v>290.20999999999998</v>
-      </c>
-      <c r="E8" s="15">
-        <v>290.20999999999998</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="15">
-        <v>694.28</v>
-      </c>
-      <c r="H8" s="15">
-        <v>549</v>
-      </c>
-      <c r="I8" s="16">
-        <v>0.85109999999999997</v>
-      </c>
-      <c r="J8" s="15">
-        <v>867.45</v>
-      </c>
-      <c r="K8" s="15">
-        <v>719.94</v>
-      </c>
-      <c r="L8" s="17">
-        <v>0.79510000000000003</v>
+      <c r="D11" s="9">
+        <v>438.48</v>
+      </c>
+      <c r="E11" s="9">
+        <v>305.45</v>
+      </c>
+      <c r="F11" s="30">
+        <v>0.94679999999999997</v>
+      </c>
+      <c r="G11" s="9">
+        <v>1007.93</v>
+      </c>
+      <c r="H11" s="9">
+        <v>821.62</v>
+      </c>
+      <c r="I11" s="30">
+        <v>0.32940000000000003</v>
+      </c>
+      <c r="J11" s="9">
+        <v>1052.72</v>
+      </c>
+      <c r="K11" s="9">
+        <v>803.9</v>
+      </c>
+      <c r="L11" s="30">
+        <v>0.59950000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="12">
-        <v>241.11</v>
-      </c>
-      <c r="E9" s="12">
-        <v>241.11</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="12">
-        <v>579.30999999999995</v>
-      </c>
-      <c r="H9" s="12">
-        <v>445.11</v>
-      </c>
-      <c r="I9" s="12">
-        <v>0.89890000000000003</v>
-      </c>
-      <c r="J9" s="12">
-        <v>519.91999999999996</v>
-      </c>
-      <c r="K9" s="12">
-        <v>405.81</v>
-      </c>
-      <c r="L9" s="13">
-        <v>0.9254</v>
+    <row r="12" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="23"/>
+      <c r="B12" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="7">
+        <v>432.52</v>
+      </c>
+      <c r="E12" s="7">
+        <v>269.81</v>
+      </c>
+      <c r="F12" s="29">
+        <v>0.94769999999999999</v>
+      </c>
+      <c r="G12" s="7">
+        <v>551.73</v>
+      </c>
+      <c r="H12" s="7">
+        <v>357.52</v>
+      </c>
+      <c r="I12" s="29">
+        <v>0.91649999999999998</v>
+      </c>
+      <c r="J12" s="7">
+        <v>588.91</v>
+      </c>
+      <c r="K12" s="34">
+        <v>383.08</v>
+      </c>
+      <c r="L12" s="29">
+        <v>0.90369999999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="7" t="s">
+    <row r="13" spans="1:13" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="23"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="8">
-        <v>432.05</v>
-      </c>
-      <c r="E10" s="8">
-        <v>295.83999999999997</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0.94830000000000003</v>
-      </c>
-      <c r="G10" s="8">
-        <v>614</v>
-      </c>
-      <c r="H10" s="8">
-        <v>516.67999999999995</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0.74709999999999999</v>
-      </c>
-      <c r="J10" s="8">
-        <v>911.19</v>
-      </c>
-      <c r="K10" s="8">
-        <v>694.07</v>
-      </c>
-      <c r="L10" s="10">
-        <v>0.69989999999999997</v>
-      </c>
+      <c r="D13" s="9">
+        <v>474.16</v>
+      </c>
+      <c r="E13" s="9">
+        <v>303.63</v>
+      </c>
+      <c r="F13" s="30">
+        <v>0.93799999999999994</v>
+      </c>
+      <c r="G13" s="9">
+        <v>568.30999999999995</v>
+      </c>
+      <c r="H13" s="9">
+        <v>365.98</v>
+      </c>
+      <c r="I13" s="30">
+        <v>0.91149999999999998</v>
+      </c>
+      <c r="J13" s="32">
+        <v>575.89</v>
+      </c>
+      <c r="K13" s="9">
+        <v>384.95</v>
+      </c>
+      <c r="L13" s="33">
+        <v>0.90839999999999999</v>
+      </c>
+      <c r="M13" s="12"/>
     </row>
-    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="12">
-        <v>438.48</v>
-      </c>
-      <c r="E11" s="12">
-        <v>305.45</v>
-      </c>
-      <c r="F11" s="12">
-        <v>0.94679999999999997</v>
-      </c>
-      <c r="G11" s="12">
-        <v>1007.93</v>
-      </c>
-      <c r="H11" s="12">
-        <v>821.62</v>
-      </c>
-      <c r="I11" s="12">
-        <v>0.32940000000000003</v>
-      </c>
-      <c r="J11" s="12">
-        <v>1052.72</v>
-      </c>
-      <c r="K11" s="12">
-        <v>803.9</v>
-      </c>
-      <c r="L11" s="13">
-        <v>0.59950000000000003</v>
+    <row r="14" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="23"/>
+      <c r="B14" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="11">
+        <v>437.06</v>
+      </c>
+      <c r="E14" s="11">
+        <v>271.70999999999998</v>
+      </c>
+      <c r="F14" s="31">
+        <v>0.9466</v>
+      </c>
+      <c r="G14" s="11">
+        <v>545.96</v>
+      </c>
+      <c r="H14" s="11">
+        <v>345.86</v>
+      </c>
+      <c r="I14" s="31">
+        <v>0.91839999999999999</v>
+      </c>
+      <c r="J14" s="11">
+        <v>608.64</v>
+      </c>
+      <c r="K14" s="11">
+        <v>384.02</v>
+      </c>
+      <c r="L14" s="31">
+        <v>0.89649999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="19"/>
-      <c r="B12" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="7" t="s">
+    <row r="15" spans="1:13" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="24"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="8">
-        <v>432.52</v>
-      </c>
-      <c r="E12" s="8">
-        <v>269.81</v>
-      </c>
-      <c r="F12" s="8">
-        <v>0.94769999999999999</v>
-      </c>
-      <c r="G12" s="8">
-        <v>551.73</v>
-      </c>
-      <c r="H12" s="8">
-        <v>357.52</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0.91649999999999998</v>
-      </c>
-      <c r="J12" s="8">
-        <v>588.91</v>
-      </c>
-      <c r="K12" s="8">
-        <v>383.08</v>
-      </c>
-      <c r="L12" s="10">
-        <v>0.90369999999999995</v>
+      <c r="D15" s="9">
+        <v>435.65</v>
+      </c>
+      <c r="E15" s="9">
+        <v>269.14</v>
+      </c>
+      <c r="F15" s="30">
+        <v>0.94740000000000002</v>
+      </c>
+      <c r="G15" s="32">
+        <v>521.72</v>
+      </c>
+      <c r="H15" s="32">
+        <v>320.33999999999997</v>
+      </c>
+      <c r="I15" s="33">
+        <v>0.92530000000000001</v>
+      </c>
+      <c r="J15" s="9">
+        <v>601.22</v>
+      </c>
+      <c r="K15" s="9">
+        <v>385.8</v>
+      </c>
+      <c r="L15" s="30">
+        <v>0.9</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="19"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="12">
+    <row r="16" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="34">
+        <v>350.76</v>
+      </c>
+      <c r="E16" s="7">
+        <v>223.65</v>
+      </c>
+      <c r="F16" s="35">
+        <v>0.96530000000000005</v>
+      </c>
+      <c r="G16" s="7">
+        <v>562.19000000000005</v>
+      </c>
+      <c r="H16" s="7">
+        <v>358.47</v>
+      </c>
+      <c r="I16" s="29">
+        <v>0.91320000000000001</v>
+      </c>
+      <c r="J16" s="34">
+        <v>588.77</v>
+      </c>
+      <c r="K16" s="7">
+        <v>376.78</v>
+      </c>
+      <c r="L16" s="35">
+        <v>0.9032</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="23"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="9">
+        <v>352.36</v>
+      </c>
+      <c r="E17" s="32">
+        <v>221.34</v>
+      </c>
+      <c r="F17" s="30">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="G17" s="32">
+        <v>509.47</v>
+      </c>
+      <c r="H17" s="32">
+        <v>326.26</v>
+      </c>
+      <c r="I17" s="33">
+        <v>0.92849999999999999</v>
+      </c>
+      <c r="J17" s="9">
+        <v>593.83000000000004</v>
+      </c>
+      <c r="K17" s="32">
+        <v>366.55</v>
+      </c>
+      <c r="L17" s="30">
+        <v>0.90129999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="23"/>
+      <c r="B18" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="7">
+        <v>361.74</v>
+      </c>
+      <c r="E18" s="7">
+        <v>240.68</v>
+      </c>
+      <c r="F18" s="29">
+        <v>0.96309999999999996</v>
+      </c>
+      <c r="G18" s="7">
+        <v>551.54</v>
+      </c>
+      <c r="H18" s="7">
+        <v>385.89</v>
+      </c>
+      <c r="I18" s="29">
+        <v>0.91659999999999997</v>
+      </c>
+      <c r="J18" s="7">
+        <v>638.69000000000005</v>
+      </c>
+      <c r="K18" s="7">
         <v>474.16</v>
       </c>
-      <c r="E13" s="12">
-        <v>303.63</v>
-      </c>
-      <c r="F13" s="12">
-        <v>0.93799999999999994</v>
-      </c>
-      <c r="G13" s="12">
-        <v>568.30999999999995</v>
-      </c>
-      <c r="H13" s="12">
-        <v>365.98</v>
-      </c>
-      <c r="I13" s="12">
-        <v>0.91149999999999998</v>
-      </c>
-      <c r="J13" s="12">
-        <v>575.89</v>
-      </c>
-      <c r="K13" s="12">
-        <v>384.95</v>
-      </c>
-      <c r="L13" s="13">
-        <v>0.90839999999999999</v>
-      </c>
-      <c r="M13" s="33"/>
+      <c r="L18" s="29">
+        <v>0.88770000000000004</v>
+      </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="19"/>
-      <c r="B14" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="14" t="s">
+    <row r="19" spans="1:12" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="24"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="15">
-        <v>437.06</v>
-      </c>
-      <c r="E14" s="15">
-        <v>271.70999999999998</v>
-      </c>
-      <c r="F14" s="15">
-        <v>0.9466</v>
-      </c>
-      <c r="G14" s="15">
-        <v>545.96</v>
-      </c>
-      <c r="H14" s="15">
-        <v>345.86</v>
-      </c>
-      <c r="I14" s="16">
-        <v>0.91839999999999999</v>
-      </c>
-      <c r="J14" s="15">
-        <v>608.64</v>
-      </c>
-      <c r="K14" s="15">
-        <v>384.02</v>
-      </c>
-      <c r="L14" s="17">
-        <v>0.89649999999999996</v>
+      <c r="D19" s="9">
+        <v>366.13</v>
+      </c>
+      <c r="E19" s="9">
+        <v>242.9</v>
+      </c>
+      <c r="F19" s="30">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="G19" s="9">
+        <v>516.74</v>
+      </c>
+      <c r="H19" s="9">
+        <v>369.44</v>
+      </c>
+      <c r="I19" s="30">
+        <v>0.92700000000000005</v>
+      </c>
+      <c r="J19" s="9">
+        <v>613.73</v>
+      </c>
+      <c r="K19" s="9">
+        <v>446.68</v>
+      </c>
+      <c r="L19" s="30">
+        <v>0.89639999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="20"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="12">
-        <v>435.65</v>
-      </c>
-      <c r="E15" s="12">
-        <v>269.14</v>
-      </c>
-      <c r="F15" s="12">
-        <v>0.94740000000000002</v>
-      </c>
-      <c r="G15" s="12">
-        <v>521.72</v>
-      </c>
-      <c r="H15" s="12">
-        <v>320.33999999999997</v>
-      </c>
-      <c r="I15" s="12">
-        <v>0.92530000000000001</v>
-      </c>
-      <c r="J15" s="12">
-        <v>601.22</v>
-      </c>
-      <c r="K15" s="12">
-        <v>385.8</v>
-      </c>
-      <c r="L15" s="13">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="8">
-        <v>350.76</v>
-      </c>
-      <c r="E16" s="8">
-        <v>223.65</v>
-      </c>
-      <c r="F16" s="8">
-        <v>0.96530000000000005</v>
-      </c>
-      <c r="G16" s="8">
-        <v>562.19000000000005</v>
-      </c>
-      <c r="H16" s="8">
-        <v>358.47</v>
-      </c>
-      <c r="I16" s="9">
-        <v>0.91320000000000001</v>
-      </c>
-      <c r="J16" s="8">
-        <v>588.77</v>
-      </c>
-      <c r="K16" s="8">
-        <v>376.78</v>
-      </c>
-      <c r="L16" s="10">
-        <v>0.9032</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="19"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="12">
-        <v>352.36</v>
-      </c>
-      <c r="E17" s="12">
-        <v>221.34</v>
-      </c>
-      <c r="F17" s="12">
-        <v>0.96499999999999997</v>
-      </c>
-      <c r="G17" s="12">
-        <v>509.47</v>
-      </c>
-      <c r="H17" s="12">
-        <v>326.26</v>
-      </c>
-      <c r="I17" s="12">
-        <v>0.92849999999999999</v>
-      </c>
-      <c r="J17" s="12">
-        <v>593.83000000000004</v>
-      </c>
-      <c r="K17" s="12">
-        <v>366.55</v>
-      </c>
-      <c r="L17" s="13">
-        <v>0.90129999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="19"/>
-      <c r="B18" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="8">
-        <v>361.74</v>
-      </c>
-      <c r="E18" s="8">
-        <v>240.68</v>
-      </c>
-      <c r="F18" s="8">
-        <v>0.96309999999999996</v>
-      </c>
-      <c r="G18" s="8">
-        <v>551.54</v>
-      </c>
-      <c r="H18" s="8">
-        <v>385.89</v>
-      </c>
-      <c r="I18" s="9">
-        <v>0.91659999999999997</v>
-      </c>
-      <c r="J18" s="8">
-        <v>638.69000000000005</v>
-      </c>
-      <c r="K18" s="8">
-        <v>474.16</v>
-      </c>
-      <c r="L18" s="10">
-        <v>0.88770000000000004</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="20"/>
-      <c r="B19" s="22"/>
-      <c r="C19" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="12">
-        <v>366.13</v>
-      </c>
-      <c r="E19" s="12">
-        <v>242.9</v>
-      </c>
-      <c r="F19" s="12">
-        <v>0.96299999999999997</v>
-      </c>
-      <c r="G19" s="12">
-        <v>516.74</v>
-      </c>
-      <c r="H19" s="12">
-        <v>369.44</v>
-      </c>
-      <c r="I19" s="12">
-        <v>0.92700000000000005</v>
-      </c>
-      <c r="J19" s="12">
-        <v>613.73</v>
-      </c>
-      <c r="K19" s="12">
-        <v>446.68</v>
-      </c>
-      <c r="L19" s="13">
-        <v>0.89639999999999997</v>
-      </c>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B18:B19"/>
@@ -1589,11 +2731,48 @@
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B14:B15"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D3:E19 G3:H19 J3:K19">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
-      <formula>400</formula>
-    </cfRule>
+  <conditionalFormatting sqref="D3:D19">
+    <cfRule type="top10" dxfId="31" priority="17" bottom="1" rank="1"/>
+    <cfRule type="top10" dxfId="30" priority="26" bottom="1" rank="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E19">
+    <cfRule type="top10" dxfId="29" priority="15" bottom="1" rank="1"/>
+    <cfRule type="top10" dxfId="28" priority="16" bottom="1" rank="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G19">
+    <cfRule type="top10" dxfId="27" priority="13" bottom="1" rank="1"/>
+    <cfRule type="top10" dxfId="26" priority="14" bottom="1" rank="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H19">
+    <cfRule type="top10" dxfId="25" priority="11" bottom="1" rank="1"/>
+    <cfRule type="top10" dxfId="24" priority="12" bottom="1" rank="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:J19">
+    <cfRule type="top10" dxfId="23" priority="9" bottom="1" rank="1"/>
+    <cfRule type="top10" dxfId="22" priority="10" bottom="1" rank="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K19">
+    <cfRule type="top10" dxfId="21" priority="7" bottom="1" rank="1"/>
+    <cfRule type="top10" dxfId="20" priority="8" bottom="1" rank="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F19">
+    <cfRule type="top10" dxfId="19" priority="5" rank="1"/>
+    <cfRule type="top10" dxfId="18" priority="6" rank="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3:I19">
+    <cfRule type="top10" dxfId="3" priority="3" rank="1"/>
+    <cfRule type="top10" dxfId="2" priority="4" rank="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L19">
+    <cfRule type="top10" dxfId="1" priority="1" rank="1"/>
+    <cfRule type="top10" dxfId="0" priority="2" rank="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
